--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487412_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487412_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8944</v>
+        <v>9.446999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.091200000000001</v>
+        <v>6.0181</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8031</v>
+        <v>3.4289</v>
       </c>
       <c r="G2" t="n">
         <v>6.4549</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5938</v>
+        <v>2.1464</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7305</v>
+        <v>1.6574</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8633</v>
+        <v>0.489</v>
       </c>
       <c r="V2" t="n">
         <v>1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.909</v>
+        <v>8.817299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1365</v>
+        <v>6.724</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7725</v>
+        <v>2.0932</v>
       </c>
       <c r="G3" t="n">
         <v>6.1991</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.486</v>
+        <v>0.4223</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.6693</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5678</v>
+        <v>-0.247</v>
       </c>
       <c r="V3" t="n">
         <v>1.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6757</v>
+        <v>7.7215</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9947</v>
+        <v>5.0939</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6811</v>
+        <v>2.6276</v>
       </c>
       <c r="G4" t="n">
         <v>5.7167</v>
@@ -766,13 +766,13 @@
         <v>3.1336</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2956</v>
+        <v>0.7502</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4817</v>
+        <v>0.6175</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1861</v>
+        <v>0.1326</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1016</v>
+        <v>6.7292</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2714</v>
+        <v>4.9475</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8301</v>
+        <v>1.7817</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8218</v>
+        <v>5.1401</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2797</v>
+        <v>2.7452</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5421</v>
+        <v>2.3949</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0272</v>
+        <v>4.6933</v>
       </c>
       <c r="K5" t="n">
-        <v>1.138</v>
+        <v>2.739</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8891</v>
+        <v>1.9544</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7946</v>
+        <v>0.4467</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1416</v>
+        <v>0.0062</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6529</v>
+        <v>0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1336</v>
+        <v>-1.1751</v>
       </c>
       <c r="R5" t="n">
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>0.63</v>
+        <v>0.7469</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6693</v>
+        <v>1.4868</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0393</v>
+        <v>-0.7399</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4332</v>
+        <v>-0.3329</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7086</v>
+        <v>-0.0576</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2754</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0301</v>
+        <v>6.3241</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4623</v>
+        <v>2.6543</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5678</v>
+        <v>3.6698</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1401</v>
+        <v>3.8218</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7452</v>
+        <v>1.2797</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3949</v>
+        <v>2.5421</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6933</v>
+        <v>2.0272</v>
       </c>
       <c r="K6" t="n">
-        <v>2.739</v>
+        <v>1.138</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9544</v>
+        <v>0.8891</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4467</v>
+        <v>1.7946</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0062</v>
+        <v>0.1416</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4405</v>
+        <v>1.6529</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1751</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R6" t="n">
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0479</v>
+        <v>0.8525</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0016</v>
+        <v>1.0522</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9537</v>
+        <v>-0.1997</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3329</v>
+        <v>2.4332</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0576</v>
+        <v>2.7086</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2754</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.1441</v>
+        <v>4.2326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7393</v>
+        <v>1.1486</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4048</v>
+        <v>3.084</v>
       </c>
       <c r="G7" t="n">
         <v>5.0455</v>
@@ -1000,13 +1000,13 @@
         <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2149</v>
+        <v>0.3035</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4158</v>
+        <v>-0.0065</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6307</v>
+        <v>0.31</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3329</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9631</v>
+        <v>1.5537</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9797</v>
+        <v>1.5703</v>
       </c>
       <c r="F8" t="n">
         <v>-0.0166</v>
@@ -1078,10 +1078,10 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6822</v>
+        <v>0.2729</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6822</v>
+        <v>0.2729</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0632</v>
+        <v>1.0097</v>
       </c>
       <c r="E9" t="n">
         <v>1.8215</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7583</v>
+        <v>-0.8118</v>
       </c>
       <c r="G9" t="n">
         <v>1.9414</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1426</v>
+        <v>0.0891</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2614</v>
+        <v>0.2079</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BUENO DE LA ROSA</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2326</v>
+        <v>0.3549</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1745</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9418</v>
+        <v>1.3312</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0214</v>
+        <v>0.8114</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2719</v>
+        <v>0.4373</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2933</v>
+        <v>0.3741</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2933</v>
+        <v>1.0521</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.8404</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2933</v>
+        <v>0.2117</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2719</v>
+        <v>-0.2407</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2719</v>
+        <v>-0.4031</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.1624</v>
       </c>
       <c r="P11" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1958</v>
+        <v>3.3294</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.101</v>
+        <v>0.5643</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1188</v>
+        <v>0.8299</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0178</v>
+        <v>-0.2655</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8837</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>J. BUENO DE LA ROSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4286</v>
+        <v>0.2594</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3856</v>
+        <v>1.1745</v>
       </c>
       <c r="F12" t="n">
-        <v>0.957</v>
+        <v>-0.9151</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8114</v>
+        <v>1.0214</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4373</v>
+        <v>-0.2719</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3741</v>
+        <v>1.2933</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0521</v>
+        <v>1.2933</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8404</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2117</v>
+        <v>1.2933</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2407</v>
+        <v>-0.2719</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4031</v>
+        <v>-0.2719</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.3294</v>
+        <v>0.1958</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2193</v>
+        <v>-0.0743</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4205</v>
+        <v>-0.1188</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6398</v>
+        <v>0.0446</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.492</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3756</v>
+        <v>-1.3489</v>
       </c>
       <c r="E13" t="n">
         <v>-0.9768</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3988</v>
+        <v>-0.3721</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4912</v>
@@ -1468,13 +1468,13 @@
         <v>0.1958</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.101</v>
+        <v>-0.0743</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>44.62479999999999</v>
+        <v>45.5157</v>
       </c>
       <c r="E14" t="n">
-        <v>28.9364</v>
+        <v>29.8273</v>
       </c>
       <c r="F14" t="n">
-        <v>15.6884</v>
+        <v>15.6883</v>
       </c>
       <c r="G14" t="n">
         <v>35.6124</v>
@@ -1528,16 +1528,16 @@
         <v>14.6717</v>
       </c>
       <c r="M14" t="n">
-        <v>5.3166</v>
+        <v>5.316600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9794</v>
+        <v>-0.9793999999999998</v>
       </c>
       <c r="O14" t="n">
         <v>6.2958</v>
       </c>
       <c r="P14" t="n">
-        <v>0.979</v>
+        <v>0.9790000000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.6263</v>
@@ -1546,13 +1546,13 @@
         <v>18.6055</v>
       </c>
       <c r="S14" t="n">
-        <v>5.0491</v>
+        <v>5.9401</v>
       </c>
       <c r="T14" t="n">
-        <v>5.2725</v>
+        <v>6.163699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2235</v>
+        <v>-0.2233999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.984</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4029</v>
+        <v>1.1765</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0411</v>
+        <v>3.3714</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4439</v>
+        <v>-2.195</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6358</v>
@@ -1624,13 +1624,13 @@
         <v>3.3294</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2371</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4498</v>
+        <v>-0.1194</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7874</v>
+        <v>-0.5384</v>
       </c>
       <c r="V15" t="n">
         <v>3.0991</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2821</v>
+        <v>-1.567</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0372</v>
+        <v>-1.2419</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2449</v>
+        <v>-0.3251</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0922</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3976</v>
+        <v>0.1128</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5634</v>
+        <v>0.3588</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1658</v>
+        <v>-0.246</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4289</v>
+        <v>-1.6796</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9702</v>
+        <v>0.6632</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3991</v>
+        <v>-2.3429</v>
       </c>
       <c r="G17" t="n">
         <v>-3.0784</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5463</v>
+        <v>-0.7971</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2682</v>
+        <v>-0.5752</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2781</v>
+        <v>-0.2219</v>
       </c>
       <c r="V17" t="n">
         <v>1.2166</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8115</v>
+        <v>-2.156</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0663</v>
+        <v>-1.657</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7452</v>
+        <v>-0.499</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5939</v>
@@ -1936,13 +1936,13 @@
         <v>2.3502</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.493</v>
+        <v>0.1625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2923</v>
+        <v>0.117</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2007</v>
+        <v>0.0454</v>
       </c>
       <c r="V19" t="n">
         <v>0.8837</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0966</v>
+        <v>-3.7327</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5648</v>
+        <v>-1.2812</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5318</v>
+        <v>-2.4516</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6918</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9074</v>
+        <v>0.2713</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1269</v>
+        <v>0.4105</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9412</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9652</v>
+        <v>-3.8583</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2909</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6742</v>
+        <v>-2.5673</v>
       </c>
       <c r="G21" t="n">
         <v>-2.831</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5051</v>
+        <v>-0.3982</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0129</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4921</v>
+        <v>-0.3852</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9961</v>
+        <v>-4.6264</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0756</v>
+        <v>-0.1529</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9205</v>
+        <v>-4.4736</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.013</v>
+        <v>-0.5923</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2399</v>
+        <v>2.065</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7731</v>
+        <v>-2.6574</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9974</v>
+        <v>2.2367</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3556</v>
+        <v>2.8785</v>
       </c>
       <c r="L22" t="n">
         <v>-0.6418</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0156</v>
+        <v>-2.829</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8843</v>
+        <v>-0.8135</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1313</v>
+        <v>-2.0156</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7419</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-1.208</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4158</v>
+        <v>-0.4311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1008</v>
+        <v>-0.7769</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2754</v>
+        <v>-2.0427</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0745</v>
+        <v>-4.8403</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3576</v>
+        <v>-3.9733</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7169</v>
+        <v>-0.8671</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5923</v>
+        <v>-2.013</v>
       </c>
       <c r="H23" t="n">
-        <v>2.065</v>
+        <v>-1.2399</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6574</v>
+        <v>-0.7731</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2367</v>
+        <v>-0.9974</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8785</v>
+        <v>-0.3556</v>
       </c>
       <c r="L23" t="n">
         <v>-0.6418</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.829</v>
+        <v>-1.0156</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8135</v>
+        <v>-0.8843</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0156</v>
+        <v>-0.1313</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7834</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6561</v>
+        <v>-0.3608</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6358</v>
+        <v>-0.3135</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0203</v>
+        <v>-0.0473</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0427</v>
+        <v>0.2754</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.0427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>A. GOMEZ LLANES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1615</v>
+        <v>-5.1422</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3747</v>
+        <v>-1.9475</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7868</v>
+        <v>-3.1947</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.1196</v>
+        <v>-2.7168</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7904</v>
+        <v>-2.4379</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3292</v>
+        <v>-0.2788</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4073</v>
+        <v>0.5738</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2094</v>
+        <v>-1.5567</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.198</v>
+        <v>2.1305</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.7123</v>
+        <v>-3.2905</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.5811</v>
+        <v>-0.8812</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1312</v>
+        <v>-2.4093</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1751</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1336</v>
+        <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3913</v>
+        <v>-0.3091</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7158</v>
+        <v>0.1411</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3244</v>
+        <v>-0.4502</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6083</v>
+        <v>-0.9412</v>
       </c>
       <c r="W24" t="n">
         <v>0.2754</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. GOMEZ LLANES</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2282</v>
+        <v>-5.5846</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3568</v>
+        <v>-2.8864</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8713</v>
+        <v>-2.6982</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7168</v>
+        <v>-6.1196</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4379</v>
+        <v>-2.7904</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2788</v>
+        <v>-3.3292</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5738</v>
+        <v>-1.4073</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5567</v>
+        <v>-0.2094</v>
       </c>
       <c r="L25" t="n">
-        <v>2.1305</v>
+        <v>-1.198</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2905</v>
+        <v>-4.7123</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8812</v>
+        <v>-2.5811</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.4093</v>
+        <v>-2.1312</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1751</v>
+        <v>1.1751</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7626</v>
+        <v>3.1336</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3951</v>
+        <v>-0.0318</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2682</v>
+        <v>0.2041</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1269</v>
+        <v>-0.2358</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9412</v>
+        <v>-0.6083</v>
       </c>
       <c r="W25" t="n">
         <v>0.2754</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.32</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5392</v>
+        <v>-3.2556</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.7807</v>
+        <v>-5.4544</v>
       </c>
       <c r="G26" t="n">
         <v>-8.880000000000001</v>
@@ -2482,13 +2482,13 @@
         <v>2.546</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7226</v>
+        <v>0.3326</v>
       </c>
       <c r="T26" t="n">
-        <v>1.2792</v>
+        <v>0.5628</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5566</v>
+        <v>-0.2302</v>
       </c>
       <c r="V26" t="n">
         <v>-2.7086</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-44.6247</v>
+        <v>-42.5778</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.6883</v>
+        <v>-15.6886</v>
       </c>
       <c r="F27" t="n">
-        <v>-28.9361</v>
+        <v>-26.8897</v>
       </c>
       <c r="G27" t="n">
         <v>-35.6123</v>
@@ -2536,7 +2536,7 @@
         <v>-5.316599999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9790999999999999</v>
+        <v>0.9790999999999994</v>
       </c>
       <c r="L27" t="n">
         <v>-6.2958</v>
@@ -2560,19 +2560,19 @@
         <v>17.6261</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.0492</v>
+        <v>-3.002400000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2234999999999996</v>
+        <v>0.2233999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.272499999999999</v>
+        <v>-3.2257</v>
       </c>
       <c r="V27" t="n">
         <v>-2.9838</v>
       </c>
       <c r="W27" t="n">
-        <v>8.0108</v>
+        <v>8.010800000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-10.9945</v>
